--- a/artfynd/A 40428-2023 artfynd.xlsx
+++ b/artfynd/A 40428-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ4"/>
+  <dimension ref="A1:AZ29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,60 +680,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119454343</v>
+        <v>136944617</v>
       </c>
       <c r="B2" t="n">
-        <v>57945</v>
+        <v>97590</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100110</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gråspett</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picus canus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>J.F. Gmelin, 1788</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Märabäcksvägen, Navarn, Mpd</t>
+          <t>Märabäcken, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>585609</v>
+        <v>586104</v>
       </c>
       <c r="R2" t="n">
-        <v>6942418</v>
+        <v>6942073</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -757,17 +745,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-08-31</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-08-31</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Vid gammalt boträd.</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,74 +765,62 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Peter Berglund</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Peter Berglund</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119454343</t>
+          <t>https://artportalen.se/Sighting/136944617</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121106226</v>
+        <v>136934804</v>
       </c>
       <c r="B3" t="n">
-        <v>57132</v>
+        <v>92384</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102612</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Märabäcksvägen, Navarn, Mpd</t>
+          <t>Märabacken, Märabacken, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>585609</v>
+        <v>585805</v>
       </c>
       <c r="R3" t="n">
-        <v>6942418</v>
+        <v>6942142</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -876,12 +847,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-11-09</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-11-09</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -896,27 +867,27 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Peter Berglund</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Peter Berglund</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121106226</t>
+          <t>https://artportalen.se/Sighting/136934804</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121106228</v>
+        <v>136935406</v>
       </c>
       <c r="B4" t="n">
-        <v>58114</v>
+        <v>92384</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -924,46 +895,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>658</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Märabäcksvägen, Navarn, Mpd</t>
+          <t>Märabacken, Märabacken, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>585609</v>
+        <v>586035</v>
       </c>
       <c r="R4" t="n">
-        <v>6942418</v>
+        <v>6942125</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -990,12 +949,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-11-09</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-11-09</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1010,18 +969,2633 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Peter Berglund</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Peter Berglund</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/136935406</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>136935458</v>
+      </c>
+      <c r="B5" t="n">
+        <v>92113</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Märabacken, Märabacken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>586037</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6942118</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Holm</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136935458</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>136935719</v>
+      </c>
+      <c r="B6" t="n">
+        <v>92113</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Märabacken, Märabacken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>586064</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6942107</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Holm</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136935719</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>136935946</v>
+      </c>
+      <c r="B7" t="n">
+        <v>92113</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Märabacken, Märabacken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>586094</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6942068</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Holm</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136935946</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>136935701</v>
+      </c>
+      <c r="B8" t="n">
+        <v>92545</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Hermanssonia centrifuga</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Märabacken, Märabacken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>586070</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6942101</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Holm</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136935701</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>136933750</v>
+      </c>
+      <c r="B9" t="n">
+        <v>79476</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Märabacken, Märabacken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>585612</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6942351</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Holm</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136933750</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>136933934</v>
+      </c>
+      <c r="B10" t="n">
+        <v>79476</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Märabacken, Märabacken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>585648</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6942295</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Holm</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136933934</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>136934223</v>
+      </c>
+      <c r="B11" t="n">
+        <v>79476</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Märabacken, Märabacken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>585673</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6942285</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Holm</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136934223</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>136934434</v>
+      </c>
+      <c r="B12" t="n">
+        <v>79476</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Märabacken, Märabacken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>585702</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6942260</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Holm</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136934434</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>136934718</v>
+      </c>
+      <c r="B13" t="n">
+        <v>79476</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Märabacken, Märabacken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>585781</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6942172</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Holm</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136934718</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>136934843</v>
+      </c>
+      <c r="B14" t="n">
+        <v>79476</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Märabacken, Märabacken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>585823</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6942123</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Holm</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136934843</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>136935767</v>
+      </c>
+      <c r="B15" t="n">
+        <v>79476</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Märabacken, Märabacken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>586071</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6942080</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Holm</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136935767</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>136944622</v>
+      </c>
+      <c r="B16" t="n">
+        <v>79476</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Märabäcken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>586141</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6942016</v>
+      </c>
+      <c r="S16" t="n">
+        <v>25</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Holm</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136944622</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>136933806</v>
+      </c>
+      <c r="B17" t="n">
+        <v>79233</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Märabacken, Märabacken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>585607</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6942343</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Holm</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136933806</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>136934028</v>
+      </c>
+      <c r="B18" t="n">
+        <v>80591</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Märabacken, Märabacken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>585673</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6942284</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Holm</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136934028</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>136934747</v>
+      </c>
+      <c r="B19" t="n">
+        <v>80591</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Märabacken, Märabacken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>585799</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6942151</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Holm</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136934747</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>136944620</v>
+      </c>
+      <c r="B20" t="n">
+        <v>80591</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Märabäcken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>586165</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6942022</v>
+      </c>
+      <c r="S20" t="n">
+        <v>25</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Holm</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136944620</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>136935112</v>
+      </c>
+      <c r="B21" t="n">
+        <v>58008</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Märabacken, Märabacken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>585876</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6942102</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Holm</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136935112</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>119454343</v>
+      </c>
+      <c r="B22" t="n">
+        <v>57945</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>100110</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Gråspett</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Picus canus</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>J.F. Gmelin, 1788</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Märabäcksvägen, Navarn, Mpd</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>585609</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6942418</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Holm</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2024-08-31</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2024-08-31</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Vid gammalt boträd.</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Peter Berglund</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Peter Berglund</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119454343</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>136934585</v>
+      </c>
+      <c r="B23" t="n">
+        <v>57195</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Märabacken, Märabacken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>585768</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6942196</v>
+      </c>
+      <c r="S23" t="n">
+        <v>25</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Holm</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136934585</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>136944618</v>
+      </c>
+      <c r="B24" t="n">
+        <v>57195</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Märabäcken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>586128</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6942051</v>
+      </c>
+      <c r="S24" t="n">
+        <v>25</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Holm</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Tupp</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136944618</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>121106226</v>
+      </c>
+      <c r="B25" t="n">
+        <v>57132</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>102612</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Märabäcksvägen, Navarn, Mpd</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>585609</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6942418</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Holm</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2024-11-09</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2024-11-09</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Peter Berglund</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Peter Berglund</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121106226</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>121106228</v>
+      </c>
+      <c r="B26" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Märabäcksvägen, Navarn, Mpd</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>585609</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6942418</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Holm</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2024-11-09</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2024-11-09</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Peter Berglund</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Peter Berglund</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/121106228</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>136934376</v>
+      </c>
+      <c r="B27" t="n">
+        <v>58169</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Märabacken, Märabacken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>585699</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6942269</v>
+      </c>
+      <c r="S27" t="n">
+        <v>25</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Holm</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>En talltitefamilj</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136934376</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>136933740</v>
+      </c>
+      <c r="B28" t="n">
+        <v>111332</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>220240</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Linnea</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Linnaea borealis</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Märabacken, Märabacken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>585612</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6942348</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Holm</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136933740</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>136934919</v>
+      </c>
+      <c r="B29" t="n">
+        <v>98215</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Märabacken, Märabacken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>585851</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6942108</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Holm</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136934919</t>
         </is>
       </c>
     </row>
@@ -1030,6 +3604,31 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 40428-2023 artfynd.xlsx
+++ b/artfynd/A 40428-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136944617</v>
       </c>
       <c r="B2" t="n">
-        <v>97590</v>
+        <v>97596</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136934804</v>
       </c>
       <c r="B3" t="n">
-        <v>92384</v>
+        <v>92386</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136935406</v>
       </c>
       <c r="B4" t="n">
-        <v>92384</v>
+        <v>92386</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136935458</v>
       </c>
       <c r="B5" t="n">
-        <v>92113</v>
+        <v>92115</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136935719</v>
       </c>
       <c r="B6" t="n">
-        <v>92113</v>
+        <v>92115</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>136935946</v>
       </c>
       <c r="B7" t="n">
-        <v>92113</v>
+        <v>92115</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>136935701</v>
       </c>
       <c r="B8" t="n">
-        <v>92545</v>
+        <v>92547</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>136933750</v>
       </c>
       <c r="B9" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>136933934</v>
       </c>
       <c r="B10" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>136934223</v>
       </c>
       <c r="B11" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>136934434</v>
       </c>
       <c r="B12" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         <v>136934718</v>
       </c>
       <c r="B13" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1907,7 +1907,7 @@
         <v>136934843</v>
       </c>
       <c r="B14" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         <v>136935767</v>
       </c>
       <c r="B15" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2111,7 +2111,7 @@
         <v>136944622</v>
       </c>
       <c r="B16" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2213,7 +2213,7 @@
         <v>136933806</v>
       </c>
       <c r="B17" t="n">
-        <v>79233</v>
+        <v>79237</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2315,7 +2315,7 @@
         <v>136934028</v>
       </c>
       <c r="B18" t="n">
-        <v>80591</v>
+        <v>80595</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2417,7 +2417,7 @@
         <v>136934747</v>
       </c>
       <c r="B19" t="n">
-        <v>80591</v>
+        <v>80595</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2519,7 +2519,7 @@
         <v>136944620</v>
       </c>
       <c r="B20" t="n">
-        <v>80591</v>
+        <v>80595</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3400,7 +3400,7 @@
         <v>136933740</v>
       </c>
       <c r="B28" t="n">
-        <v>111332</v>
+        <v>111338</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3502,7 +3502,7 @@
         <v>136934919</v>
       </c>
       <c r="B29" t="n">
-        <v>98215</v>
+        <v>98221</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 40428-2023 artfynd.xlsx
+++ b/artfynd/A 40428-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136944617</v>
       </c>
       <c r="B2" t="n">
-        <v>97596</v>
+        <v>97598</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136934804</v>
       </c>
       <c r="B3" t="n">
-        <v>92386</v>
+        <v>92388</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136935406</v>
       </c>
       <c r="B4" t="n">
-        <v>92386</v>
+        <v>92388</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136935458</v>
       </c>
       <c r="B5" t="n">
-        <v>92115</v>
+        <v>92117</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136935719</v>
       </c>
       <c r="B6" t="n">
-        <v>92115</v>
+        <v>92117</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>136935946</v>
       </c>
       <c r="B7" t="n">
-        <v>92115</v>
+        <v>92117</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>136935701</v>
       </c>
       <c r="B8" t="n">
-        <v>92547</v>
+        <v>92549</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>136933750</v>
       </c>
       <c r="B9" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>136933934</v>
       </c>
       <c r="B10" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>136934223</v>
       </c>
       <c r="B11" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>136934434</v>
       </c>
       <c r="B12" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         <v>136934718</v>
       </c>
       <c r="B13" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1907,7 +1907,7 @@
         <v>136934843</v>
       </c>
       <c r="B14" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         <v>136935767</v>
       </c>
       <c r="B15" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2111,7 +2111,7 @@
         <v>136944622</v>
       </c>
       <c r="B16" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2213,7 +2213,7 @@
         <v>136933806</v>
       </c>
       <c r="B17" t="n">
-        <v>79237</v>
+        <v>79239</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2315,7 +2315,7 @@
         <v>136934028</v>
       </c>
       <c r="B18" t="n">
-        <v>80595</v>
+        <v>80597</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2417,7 +2417,7 @@
         <v>136934747</v>
       </c>
       <c r="B19" t="n">
-        <v>80595</v>
+        <v>80597</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2519,7 +2519,7 @@
         <v>136944620</v>
       </c>
       <c r="B20" t="n">
-        <v>80595</v>
+        <v>80597</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3400,7 +3400,7 @@
         <v>136933740</v>
       </c>
       <c r="B28" t="n">
-        <v>111338</v>
+        <v>111340</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3502,7 +3502,7 @@
         <v>136934919</v>
       </c>
       <c r="B29" t="n">
-        <v>98221</v>
+        <v>98223</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 40428-2023 artfynd.xlsx
+++ b/artfynd/A 40428-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136944617</v>
       </c>
       <c r="B2" t="n">
-        <v>97598</v>
+        <v>97599</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136934804</v>
       </c>
       <c r="B3" t="n">
-        <v>92388</v>
+        <v>92389</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136935406</v>
       </c>
       <c r="B4" t="n">
-        <v>92388</v>
+        <v>92389</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136935458</v>
       </c>
       <c r="B5" t="n">
-        <v>92117</v>
+        <v>92118</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136935719</v>
       </c>
       <c r="B6" t="n">
-        <v>92117</v>
+        <v>92118</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>136935946</v>
       </c>
       <c r="B7" t="n">
-        <v>92117</v>
+        <v>92118</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>136935701</v>
       </c>
       <c r="B8" t="n">
-        <v>92549</v>
+        <v>92550</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>136933750</v>
       </c>
       <c r="B9" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>136933934</v>
       </c>
       <c r="B10" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>136934223</v>
       </c>
       <c r="B11" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>136934434</v>
       </c>
       <c r="B12" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         <v>136934718</v>
       </c>
       <c r="B13" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1907,7 +1907,7 @@
         <v>136934843</v>
       </c>
       <c r="B14" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         <v>136935767</v>
       </c>
       <c r="B15" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2111,7 +2111,7 @@
         <v>136944622</v>
       </c>
       <c r="B16" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2213,7 +2213,7 @@
         <v>136933806</v>
       </c>
       <c r="B17" t="n">
-        <v>79239</v>
+        <v>79240</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2315,7 +2315,7 @@
         <v>136934028</v>
       </c>
       <c r="B18" t="n">
-        <v>80597</v>
+        <v>80598</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2417,7 +2417,7 @@
         <v>136934747</v>
       </c>
       <c r="B19" t="n">
-        <v>80597</v>
+        <v>80598</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2519,7 +2519,7 @@
         <v>136944620</v>
       </c>
       <c r="B20" t="n">
-        <v>80597</v>
+        <v>80598</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3400,7 +3400,7 @@
         <v>136933740</v>
       </c>
       <c r="B28" t="n">
-        <v>111340</v>
+        <v>111341</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3502,7 +3502,7 @@
         <v>136934919</v>
       </c>
       <c r="B29" t="n">
-        <v>98223</v>
+        <v>98224</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 40428-2023 artfynd.xlsx
+++ b/artfynd/A 40428-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136944617</v>
       </c>
       <c r="B2" t="n">
-        <v>97599</v>
+        <v>97605</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136934804</v>
       </c>
       <c r="B3" t="n">
-        <v>92389</v>
+        <v>92395</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136935406</v>
       </c>
       <c r="B4" t="n">
-        <v>92389</v>
+        <v>92395</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136935458</v>
       </c>
       <c r="B5" t="n">
-        <v>92118</v>
+        <v>92124</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136935719</v>
       </c>
       <c r="B6" t="n">
-        <v>92118</v>
+        <v>92124</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>136935946</v>
       </c>
       <c r="B7" t="n">
-        <v>92118</v>
+        <v>92124</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>136935701</v>
       </c>
       <c r="B8" t="n">
-        <v>92550</v>
+        <v>92556</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -3400,7 +3400,7 @@
         <v>136933740</v>
       </c>
       <c r="B28" t="n">
-        <v>111341</v>
+        <v>111347</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3502,7 +3502,7 @@
         <v>136934919</v>
       </c>
       <c r="B29" t="n">
-        <v>98224</v>
+        <v>98230</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 40428-2023 artfynd.xlsx
+++ b/artfynd/A 40428-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136944617</v>
       </c>
       <c r="B2" t="n">
-        <v>97605</v>
+        <v>97609</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136934804</v>
       </c>
       <c r="B3" t="n">
-        <v>92395</v>
+        <v>92399</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136935406</v>
       </c>
       <c r="B4" t="n">
-        <v>92395</v>
+        <v>92399</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136935458</v>
       </c>
       <c r="B5" t="n">
-        <v>92124</v>
+        <v>92128</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136935719</v>
       </c>
       <c r="B6" t="n">
-        <v>92124</v>
+        <v>92128</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>136935946</v>
       </c>
       <c r="B7" t="n">
-        <v>92124</v>
+        <v>92128</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>136935701</v>
       </c>
       <c r="B8" t="n">
-        <v>92556</v>
+        <v>92560</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>136933750</v>
       </c>
       <c r="B9" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>136933934</v>
       </c>
       <c r="B10" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>136934223</v>
       </c>
       <c r="B11" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>136934434</v>
       </c>
       <c r="B12" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         <v>136934718</v>
       </c>
       <c r="B13" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1907,7 +1907,7 @@
         <v>136934843</v>
       </c>
       <c r="B14" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         <v>136935767</v>
       </c>
       <c r="B15" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2111,7 +2111,7 @@
         <v>136944622</v>
       </c>
       <c r="B16" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2213,7 +2213,7 @@
         <v>136933806</v>
       </c>
       <c r="B17" t="n">
-        <v>79240</v>
+        <v>79242</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2315,7 +2315,7 @@
         <v>136934028</v>
       </c>
       <c r="B18" t="n">
-        <v>80598</v>
+        <v>80600</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2417,7 +2417,7 @@
         <v>136934747</v>
       </c>
       <c r="B19" t="n">
-        <v>80598</v>
+        <v>80600</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2519,7 +2519,7 @@
         <v>136944620</v>
       </c>
       <c r="B20" t="n">
-        <v>80598</v>
+        <v>80600</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3400,7 +3400,7 @@
         <v>136933740</v>
       </c>
       <c r="B28" t="n">
-        <v>111347</v>
+        <v>111351</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3502,7 +3502,7 @@
         <v>136934919</v>
       </c>
       <c r="B29" t="n">
-        <v>98230</v>
+        <v>98234</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 40428-2023 artfynd.xlsx
+++ b/artfynd/A 40428-2023 artfynd.xlsx
@@ -2728,7 +2728,7 @@
         <v>119454343</v>
       </c>
       <c r="B22" t="n">
-        <v>57945</v>
+        <v>58000</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 40428-2023 artfynd.xlsx
+++ b/artfynd/A 40428-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136944617</v>
       </c>
       <c r="B2" t="n">
-        <v>97609</v>
+        <v>97611</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -3400,7 +3400,7 @@
         <v>136933740</v>
       </c>
       <c r="B28" t="n">
-        <v>111351</v>
+        <v>111353</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3502,7 +3502,7 @@
         <v>136934919</v>
       </c>
       <c r="B29" t="n">
-        <v>98234</v>
+        <v>98236</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 40428-2023 artfynd.xlsx
+++ b/artfynd/A 40428-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136944617</v>
       </c>
       <c r="B2" t="n">
-        <v>97611</v>
+        <v>97613</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136934804</v>
       </c>
       <c r="B3" t="n">
-        <v>92399</v>
+        <v>92401</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136935406</v>
       </c>
       <c r="B4" t="n">
-        <v>92399</v>
+        <v>92401</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136935458</v>
       </c>
       <c r="B5" t="n">
-        <v>92128</v>
+        <v>92130</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136935719</v>
       </c>
       <c r="B6" t="n">
-        <v>92128</v>
+        <v>92130</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>136935946</v>
       </c>
       <c r="B7" t="n">
-        <v>92128</v>
+        <v>92130</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>136935701</v>
       </c>
       <c r="B8" t="n">
-        <v>92560</v>
+        <v>92562</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>136933750</v>
       </c>
       <c r="B9" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>136933934</v>
       </c>
       <c r="B10" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>136934223</v>
       </c>
       <c r="B11" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>136934434</v>
       </c>
       <c r="B12" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         <v>136934718</v>
       </c>
       <c r="B13" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1907,7 +1907,7 @@
         <v>136934843</v>
       </c>
       <c r="B14" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         <v>136935767</v>
       </c>
       <c r="B15" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2111,7 +2111,7 @@
         <v>136944622</v>
       </c>
       <c r="B16" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2213,7 +2213,7 @@
         <v>136933806</v>
       </c>
       <c r="B17" t="n">
-        <v>79242</v>
+        <v>79245</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2315,7 +2315,7 @@
         <v>136934028</v>
       </c>
       <c r="B18" t="n">
-        <v>80600</v>
+        <v>80603</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2417,7 +2417,7 @@
         <v>136934747</v>
       </c>
       <c r="B19" t="n">
-        <v>80600</v>
+        <v>80603</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2519,7 +2519,7 @@
         <v>136944620</v>
       </c>
       <c r="B20" t="n">
-        <v>80600</v>
+        <v>80603</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3400,7 +3400,7 @@
         <v>136933740</v>
       </c>
       <c r="B28" t="n">
-        <v>111353</v>
+        <v>111355</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3502,7 +3502,7 @@
         <v>136934919</v>
       </c>
       <c r="B29" t="n">
-        <v>98236</v>
+        <v>98238</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 40428-2023 artfynd.xlsx
+++ b/artfynd/A 40428-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136944617</v>
       </c>
       <c r="B2" t="n">
-        <v>97613</v>
+        <v>97626</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136934804</v>
       </c>
       <c r="B3" t="n">
-        <v>92401</v>
+        <v>92414</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136935406</v>
       </c>
       <c r="B4" t="n">
-        <v>92401</v>
+        <v>92414</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136935458</v>
       </c>
       <c r="B5" t="n">
-        <v>92130</v>
+        <v>92143</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136935719</v>
       </c>
       <c r="B6" t="n">
-        <v>92130</v>
+        <v>92143</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>136935946</v>
       </c>
       <c r="B7" t="n">
-        <v>92130</v>
+        <v>92143</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>136935701</v>
       </c>
       <c r="B8" t="n">
-        <v>92562</v>
+        <v>92575</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>136933750</v>
       </c>
       <c r="B9" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>136933934</v>
       </c>
       <c r="B10" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>136934223</v>
       </c>
       <c r="B11" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>136934434</v>
       </c>
       <c r="B12" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         <v>136934718</v>
       </c>
       <c r="B13" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1907,7 +1907,7 @@
         <v>136934843</v>
       </c>
       <c r="B14" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         <v>136935767</v>
       </c>
       <c r="B15" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2111,7 +2111,7 @@
         <v>136944622</v>
       </c>
       <c r="B16" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2213,7 +2213,7 @@
         <v>136933806</v>
       </c>
       <c r="B17" t="n">
-        <v>79245</v>
+        <v>79258</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2315,7 +2315,7 @@
         <v>136934028</v>
       </c>
       <c r="B18" t="n">
-        <v>80603</v>
+        <v>80616</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2417,7 +2417,7 @@
         <v>136934747</v>
       </c>
       <c r="B19" t="n">
-        <v>80603</v>
+        <v>80616</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2519,7 +2519,7 @@
         <v>136944620</v>
       </c>
       <c r="B20" t="n">
-        <v>80603</v>
+        <v>80616</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2621,7 +2621,7 @@
         <v>136935112</v>
       </c>
       <c r="B21" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2728,7 +2728,7 @@
         <v>119454343</v>
       </c>
       <c r="B22" t="n">
-        <v>58000</v>
+        <v>58013</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2847,7 +2847,7 @@
         <v>136934585</v>
       </c>
       <c r="B23" t="n">
-        <v>57195</v>
+        <v>57208</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2958,7 +2958,7 @@
         <v>136944618</v>
       </c>
       <c r="B24" t="n">
-        <v>57195</v>
+        <v>57208</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3293,7 +3293,7 @@
         <v>136934376</v>
       </c>
       <c r="B27" t="n">
-        <v>58169</v>
+        <v>58182</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3400,7 +3400,7 @@
         <v>136933740</v>
       </c>
       <c r="B28" t="n">
-        <v>111355</v>
+        <v>111368</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3502,7 +3502,7 @@
         <v>136934919</v>
       </c>
       <c r="B29" t="n">
-        <v>98238</v>
+        <v>98251</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 40428-2023 artfynd.xlsx
+++ b/artfynd/A 40428-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136944617</v>
       </c>
       <c r="B2" t="n">
-        <v>97626</v>
+        <v>97628</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136934804</v>
       </c>
       <c r="B3" t="n">
-        <v>92414</v>
+        <v>92416</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136935406</v>
       </c>
       <c r="B4" t="n">
-        <v>92414</v>
+        <v>92416</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136935458</v>
       </c>
       <c r="B5" t="n">
-        <v>92143</v>
+        <v>92145</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136935719</v>
       </c>
       <c r="B6" t="n">
-        <v>92143</v>
+        <v>92145</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>136935946</v>
       </c>
       <c r="B7" t="n">
-        <v>92143</v>
+        <v>92145</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>136935701</v>
       </c>
       <c r="B8" t="n">
-        <v>92575</v>
+        <v>92577</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>136933750</v>
       </c>
       <c r="B9" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>136933934</v>
       </c>
       <c r="B10" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>136934223</v>
       </c>
       <c r="B11" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>136934434</v>
       </c>
       <c r="B12" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         <v>136934718</v>
       </c>
       <c r="B13" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1907,7 +1907,7 @@
         <v>136934843</v>
       </c>
       <c r="B14" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         <v>136935767</v>
       </c>
       <c r="B15" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2111,7 +2111,7 @@
         <v>136944622</v>
       </c>
       <c r="B16" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2213,7 +2213,7 @@
         <v>136933806</v>
       </c>
       <c r="B17" t="n">
-        <v>79258</v>
+        <v>79260</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2315,7 +2315,7 @@
         <v>136934028</v>
       </c>
       <c r="B18" t="n">
-        <v>80616</v>
+        <v>80618</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2417,7 +2417,7 @@
         <v>136934747</v>
       </c>
       <c r="B19" t="n">
-        <v>80616</v>
+        <v>80618</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2519,7 +2519,7 @@
         <v>136944620</v>
       </c>
       <c r="B20" t="n">
-        <v>80616</v>
+        <v>80618</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2621,7 +2621,7 @@
         <v>136935112</v>
       </c>
       <c r="B21" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2728,7 +2728,7 @@
         <v>119454343</v>
       </c>
       <c r="B22" t="n">
-        <v>58013</v>
+        <v>58015</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2847,7 +2847,7 @@
         <v>136934585</v>
       </c>
       <c r="B23" t="n">
-        <v>57208</v>
+        <v>57210</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2958,7 +2958,7 @@
         <v>136944618</v>
       </c>
       <c r="B24" t="n">
-        <v>57208</v>
+        <v>57210</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3293,7 +3293,7 @@
         <v>136934376</v>
       </c>
       <c r="B27" t="n">
-        <v>58182</v>
+        <v>58184</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3400,7 +3400,7 @@
         <v>136933740</v>
       </c>
       <c r="B28" t="n">
-        <v>111368</v>
+        <v>111370</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3502,7 +3502,7 @@
         <v>136934919</v>
       </c>
       <c r="B29" t="n">
-        <v>98251</v>
+        <v>98253</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 40428-2023 artfynd.xlsx
+++ b/artfynd/A 40428-2023 artfynd.xlsx
@@ -2760,11 +2760,7 @@
       </c>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+      <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2877,11 +2873,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+      <c r="K23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Märabacken, Märabacken, Mpd</t>

--- a/artfynd/A 40428-2023 artfynd.xlsx
+++ b/artfynd/A 40428-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136944617</v>
       </c>
       <c r="B2" t="n">
-        <v>97628</v>
+        <v>97631</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136934804</v>
       </c>
       <c r="B3" t="n">
-        <v>92416</v>
+        <v>92419</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136935406</v>
       </c>
       <c r="B4" t="n">
-        <v>92416</v>
+        <v>92419</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136935458</v>
       </c>
       <c r="B5" t="n">
-        <v>92145</v>
+        <v>92148</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136935719</v>
       </c>
       <c r="B6" t="n">
-        <v>92145</v>
+        <v>92148</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>136935946</v>
       </c>
       <c r="B7" t="n">
-        <v>92145</v>
+        <v>92148</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>136935701</v>
       </c>
       <c r="B8" t="n">
-        <v>92577</v>
+        <v>92580</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -3392,7 +3392,7 @@
         <v>136933740</v>
       </c>
       <c r="B28" t="n">
-        <v>111370</v>
+        <v>111376</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3494,7 +3494,7 @@
         <v>136934919</v>
       </c>
       <c r="B29" t="n">
-        <v>98253</v>
+        <v>98256</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 40428-2023 artfynd.xlsx
+++ b/artfynd/A 40428-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136944617</v>
       </c>
       <c r="B2" t="n">
-        <v>97631</v>
+        <v>97641</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136934804</v>
       </c>
       <c r="B3" t="n">
-        <v>92419</v>
+        <v>92429</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136935406</v>
       </c>
       <c r="B4" t="n">
-        <v>92419</v>
+        <v>92429</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136935458</v>
       </c>
       <c r="B5" t="n">
-        <v>92148</v>
+        <v>92158</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136935719</v>
       </c>
       <c r="B6" t="n">
-        <v>92148</v>
+        <v>92158</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>136935946</v>
       </c>
       <c r="B7" t="n">
-        <v>92148</v>
+        <v>92158</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>136935701</v>
       </c>
       <c r="B8" t="n">
-        <v>92580</v>
+        <v>92590</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>136933750</v>
       </c>
       <c r="B9" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>136933934</v>
       </c>
       <c r="B10" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>136934223</v>
       </c>
       <c r="B11" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>136934434</v>
       </c>
       <c r="B12" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         <v>136934718</v>
       </c>
       <c r="B13" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1907,7 +1907,7 @@
         <v>136934843</v>
       </c>
       <c r="B14" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         <v>136935767</v>
       </c>
       <c r="B15" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2111,7 +2111,7 @@
         <v>136944622</v>
       </c>
       <c r="B16" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2213,7 +2213,7 @@
         <v>136933806</v>
       </c>
       <c r="B17" t="n">
-        <v>79260</v>
+        <v>79270</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2315,7 +2315,7 @@
         <v>136934028</v>
       </c>
       <c r="B18" t="n">
-        <v>80618</v>
+        <v>80628</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2417,7 +2417,7 @@
         <v>136934747</v>
       </c>
       <c r="B19" t="n">
-        <v>80618</v>
+        <v>80628</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2519,7 +2519,7 @@
         <v>136944620</v>
       </c>
       <c r="B20" t="n">
-        <v>80618</v>
+        <v>80628</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2621,7 +2621,7 @@
         <v>136935112</v>
       </c>
       <c r="B21" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2728,7 +2728,7 @@
         <v>119454343</v>
       </c>
       <c r="B22" t="n">
-        <v>58015</v>
+        <v>58025</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2843,7 +2843,7 @@
         <v>136934585</v>
       </c>
       <c r="B23" t="n">
-        <v>57210</v>
+        <v>57220</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2950,7 +2950,7 @@
         <v>136944618</v>
       </c>
       <c r="B24" t="n">
-        <v>57210</v>
+        <v>57220</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3285,7 +3285,7 @@
         <v>136934376</v>
       </c>
       <c r="B27" t="n">
-        <v>58184</v>
+        <v>58194</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3392,7 +3392,7 @@
         <v>136933740</v>
       </c>
       <c r="B28" t="n">
-        <v>111376</v>
+        <v>111398</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3494,7 +3494,7 @@
         <v>136934919</v>
       </c>
       <c r="B29" t="n">
-        <v>98256</v>
+        <v>98266</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 40428-2023 artfynd.xlsx
+++ b/artfynd/A 40428-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136944617</v>
       </c>
       <c r="B2" t="n">
-        <v>97641</v>
+        <v>97642</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136934804</v>
       </c>
       <c r="B3" t="n">
-        <v>92429</v>
+        <v>92430</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136935406</v>
       </c>
       <c r="B4" t="n">
-        <v>92429</v>
+        <v>92430</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136935458</v>
       </c>
       <c r="B5" t="n">
-        <v>92158</v>
+        <v>92159</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136935719</v>
       </c>
       <c r="B6" t="n">
-        <v>92158</v>
+        <v>92159</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>136935946</v>
       </c>
       <c r="B7" t="n">
-        <v>92158</v>
+        <v>92159</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>136935701</v>
       </c>
       <c r="B8" t="n">
-        <v>92590</v>
+        <v>92591</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -3392,7 +3392,7 @@
         <v>136933740</v>
       </c>
       <c r="B28" t="n">
-        <v>111398</v>
+        <v>111399</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3494,7 +3494,7 @@
         <v>136934919</v>
       </c>
       <c r="B29" t="n">
-        <v>98266</v>
+        <v>98267</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 40428-2023 artfynd.xlsx
+++ b/artfynd/A 40428-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136944617</v>
       </c>
       <c r="B2" t="n">
-        <v>97642</v>
+        <v>97647</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136934804</v>
       </c>
       <c r="B3" t="n">
-        <v>92430</v>
+        <v>92433</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136935406</v>
       </c>
       <c r="B4" t="n">
-        <v>92430</v>
+        <v>92433</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136935458</v>
       </c>
       <c r="B5" t="n">
-        <v>92159</v>
+        <v>92162</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136935719</v>
       </c>
       <c r="B6" t="n">
-        <v>92159</v>
+        <v>92162</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>136935946</v>
       </c>
       <c r="B7" t="n">
-        <v>92159</v>
+        <v>92162</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>136935701</v>
       </c>
       <c r="B8" t="n">
-        <v>92591</v>
+        <v>92594</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>136933750</v>
       </c>
       <c r="B9" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>136933934</v>
       </c>
       <c r="B10" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>136934223</v>
       </c>
       <c r="B11" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>136934434</v>
       </c>
       <c r="B12" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         <v>136934718</v>
       </c>
       <c r="B13" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1907,7 +1907,7 @@
         <v>136934843</v>
       </c>
       <c r="B14" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         <v>136935767</v>
       </c>
       <c r="B15" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2111,7 +2111,7 @@
         <v>136944622</v>
       </c>
       <c r="B16" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2213,7 +2213,7 @@
         <v>136933806</v>
       </c>
       <c r="B17" t="n">
-        <v>79270</v>
+        <v>79273</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2315,7 +2315,7 @@
         <v>136934028</v>
       </c>
       <c r="B18" t="n">
-        <v>80628</v>
+        <v>80631</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2417,7 +2417,7 @@
         <v>136934747</v>
       </c>
       <c r="B19" t="n">
-        <v>80628</v>
+        <v>80631</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2519,7 +2519,7 @@
         <v>136944620</v>
       </c>
       <c r="B20" t="n">
-        <v>80628</v>
+        <v>80631</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2621,7 +2621,7 @@
         <v>136935112</v>
       </c>
       <c r="B21" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2728,7 +2728,7 @@
         <v>119454343</v>
       </c>
       <c r="B22" t="n">
-        <v>58025</v>
+        <v>58026</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2843,7 +2843,7 @@
         <v>136934585</v>
       </c>
       <c r="B23" t="n">
-        <v>57220</v>
+        <v>57221</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2950,7 +2950,7 @@
         <v>136944618</v>
       </c>
       <c r="B24" t="n">
-        <v>57220</v>
+        <v>57221</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3285,7 +3285,7 @@
         <v>136934376</v>
       </c>
       <c r="B27" t="n">
-        <v>58194</v>
+        <v>58195</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3392,7 +3392,7 @@
         <v>136933740</v>
       </c>
       <c r="B28" t="n">
-        <v>111399</v>
+        <v>111404</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3494,7 +3494,7 @@
         <v>136934919</v>
       </c>
       <c r="B29" t="n">
-        <v>98267</v>
+        <v>98272</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 40428-2023 artfynd.xlsx
+++ b/artfynd/A 40428-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136944617</v>
       </c>
       <c r="B2" t="n">
-        <v>97647</v>
+        <v>97649</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136934804</v>
       </c>
       <c r="B3" t="n">
-        <v>92433</v>
+        <v>92435</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136935406</v>
       </c>
       <c r="B4" t="n">
-        <v>92433</v>
+        <v>92435</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136935458</v>
       </c>
       <c r="B5" t="n">
-        <v>92162</v>
+        <v>92164</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136935719</v>
       </c>
       <c r="B6" t="n">
-        <v>92162</v>
+        <v>92164</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>136935946</v>
       </c>
       <c r="B7" t="n">
-        <v>92162</v>
+        <v>92164</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>136935701</v>
       </c>
       <c r="B8" t="n">
-        <v>92594</v>
+        <v>92596</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -3392,7 +3392,7 @@
         <v>136933740</v>
       </c>
       <c r="B28" t="n">
-        <v>111404</v>
+        <v>111407</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3494,7 +3494,7 @@
         <v>136934919</v>
       </c>
       <c r="B29" t="n">
-        <v>98272</v>
+        <v>98274</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 40428-2023 artfynd.xlsx
+++ b/artfynd/A 40428-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136944617</v>
       </c>
       <c r="B2" t="n">
-        <v>97649</v>
+        <v>97655</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136934804</v>
       </c>
       <c r="B3" t="n">
-        <v>92435</v>
+        <v>92440</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136935406</v>
       </c>
       <c r="B4" t="n">
-        <v>92435</v>
+        <v>92440</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136935458</v>
       </c>
       <c r="B5" t="n">
-        <v>92164</v>
+        <v>92169</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136935719</v>
       </c>
       <c r="B6" t="n">
-        <v>92164</v>
+        <v>92169</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>136935946</v>
       </c>
       <c r="B7" t="n">
-        <v>92164</v>
+        <v>92169</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>136935701</v>
       </c>
       <c r="B8" t="n">
-        <v>92596</v>
+        <v>92601</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>136933750</v>
       </c>
       <c r="B9" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>136933934</v>
       </c>
       <c r="B10" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>136934223</v>
       </c>
       <c r="B11" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>136934434</v>
       </c>
       <c r="B12" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         <v>136934718</v>
       </c>
       <c r="B13" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1907,7 +1907,7 @@
         <v>136934843</v>
       </c>
       <c r="B14" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         <v>136935767</v>
       </c>
       <c r="B15" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2111,7 +2111,7 @@
         <v>136944622</v>
       </c>
       <c r="B16" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2213,7 +2213,7 @@
         <v>136933806</v>
       </c>
       <c r="B17" t="n">
-        <v>79273</v>
+        <v>79278</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2315,7 +2315,7 @@
         <v>136934028</v>
       </c>
       <c r="B18" t="n">
-        <v>80631</v>
+        <v>80636</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2417,7 +2417,7 @@
         <v>136934747</v>
       </c>
       <c r="B19" t="n">
-        <v>80631</v>
+        <v>80636</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2519,7 +2519,7 @@
         <v>136944620</v>
       </c>
       <c r="B20" t="n">
-        <v>80631</v>
+        <v>80636</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2621,7 +2621,7 @@
         <v>136935112</v>
       </c>
       <c r="B21" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2728,7 +2728,7 @@
         <v>119454343</v>
       </c>
       <c r="B22" t="n">
-        <v>58026</v>
+        <v>58027</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3285,7 +3285,7 @@
         <v>136934376</v>
       </c>
       <c r="B27" t="n">
-        <v>58195</v>
+        <v>58196</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3392,7 +3392,7 @@
         <v>136933740</v>
       </c>
       <c r="B28" t="n">
-        <v>111407</v>
+        <v>111413</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3494,7 +3494,7 @@
         <v>136934919</v>
       </c>
       <c r="B29" t="n">
-        <v>98274</v>
+        <v>98280</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 40428-2023 artfynd.xlsx
+++ b/artfynd/A 40428-2023 artfynd.xlsx
@@ -3392,7 +3392,7 @@
         <v>136933740</v>
       </c>
       <c r="B28" t="n">
-        <v>111413</v>
+        <v>111414</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 40428-2023 artfynd.xlsx
+++ b/artfynd/A 40428-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136944617</v>
       </c>
       <c r="B2" t="n">
-        <v>97655</v>
+        <v>97667</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136934804</v>
       </c>
       <c r="B3" t="n">
-        <v>92440</v>
+        <v>92452</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136935406</v>
       </c>
       <c r="B4" t="n">
-        <v>92440</v>
+        <v>92452</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136935458</v>
       </c>
       <c r="B5" t="n">
-        <v>92169</v>
+        <v>92181</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136935719</v>
       </c>
       <c r="B6" t="n">
-        <v>92169</v>
+        <v>92181</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>136935946</v>
       </c>
       <c r="B7" t="n">
-        <v>92169</v>
+        <v>92181</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>136935701</v>
       </c>
       <c r="B8" t="n">
-        <v>92601</v>
+        <v>92613</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>136933750</v>
       </c>
       <c r="B9" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>136933934</v>
       </c>
       <c r="B10" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>136934223</v>
       </c>
       <c r="B11" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>136934434</v>
       </c>
       <c r="B12" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         <v>136934718</v>
       </c>
       <c r="B13" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1907,7 +1907,7 @@
         <v>136934843</v>
       </c>
       <c r="B14" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         <v>136935767</v>
       </c>
       <c r="B15" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2111,7 +2111,7 @@
         <v>136944622</v>
       </c>
       <c r="B16" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2213,7 +2213,7 @@
         <v>136933806</v>
       </c>
       <c r="B17" t="n">
-        <v>79278</v>
+        <v>79289</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2315,7 +2315,7 @@
         <v>136934028</v>
       </c>
       <c r="B18" t="n">
-        <v>80636</v>
+        <v>80647</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2417,7 +2417,7 @@
         <v>136934747</v>
       </c>
       <c r="B19" t="n">
-        <v>80636</v>
+        <v>80647</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2519,7 +2519,7 @@
         <v>136944620</v>
       </c>
       <c r="B20" t="n">
-        <v>80636</v>
+        <v>80647</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3392,7 +3392,7 @@
         <v>136933740</v>
       </c>
       <c r="B28" t="n">
-        <v>111414</v>
+        <v>111426</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3494,7 +3494,7 @@
         <v>136934919</v>
       </c>
       <c r="B29" t="n">
-        <v>98280</v>
+        <v>98292</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 40428-2023 artfynd.xlsx
+++ b/artfynd/A 40428-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136944617</v>
       </c>
       <c r="B2" t="n">
-        <v>97667</v>
+        <v>97668</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136934804</v>
       </c>
       <c r="B3" t="n">
-        <v>92452</v>
+        <v>92453</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136935406</v>
       </c>
       <c r="B4" t="n">
-        <v>92452</v>
+        <v>92453</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136935458</v>
       </c>
       <c r="B5" t="n">
-        <v>92181</v>
+        <v>92182</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136935719</v>
       </c>
       <c r="B6" t="n">
-        <v>92181</v>
+        <v>92182</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>136935946</v>
       </c>
       <c r="B7" t="n">
-        <v>92181</v>
+        <v>92182</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>136935701</v>
       </c>
       <c r="B8" t="n">
-        <v>92613</v>
+        <v>92614</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>136933750</v>
       </c>
       <c r="B9" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>136933934</v>
       </c>
       <c r="B10" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>136934223</v>
       </c>
       <c r="B11" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>136934434</v>
       </c>
       <c r="B12" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         <v>136934718</v>
       </c>
       <c r="B13" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1907,7 +1907,7 @@
         <v>136934843</v>
       </c>
       <c r="B14" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         <v>136935767</v>
       </c>
       <c r="B15" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2111,7 +2111,7 @@
         <v>136944622</v>
       </c>
       <c r="B16" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2213,7 +2213,7 @@
         <v>136933806</v>
       </c>
       <c r="B17" t="n">
-        <v>79289</v>
+        <v>79290</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2315,7 +2315,7 @@
         <v>136934028</v>
       </c>
       <c r="B18" t="n">
-        <v>80647</v>
+        <v>80648</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2417,7 +2417,7 @@
         <v>136934747</v>
       </c>
       <c r="B19" t="n">
-        <v>80647</v>
+        <v>80648</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2519,7 +2519,7 @@
         <v>136944620</v>
       </c>
       <c r="B20" t="n">
-        <v>80647</v>
+        <v>80648</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3392,7 +3392,7 @@
         <v>136933740</v>
       </c>
       <c r="B28" t="n">
-        <v>111426</v>
+        <v>111427</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3494,7 +3494,7 @@
         <v>136934919</v>
       </c>
       <c r="B29" t="n">
-        <v>98292</v>
+        <v>98293</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 40428-2023 artfynd.xlsx
+++ b/artfynd/A 40428-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136944617</v>
       </c>
       <c r="B2" t="n">
-        <v>97668</v>
+        <v>97671</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136934804</v>
       </c>
       <c r="B3" t="n">
-        <v>92453</v>
+        <v>92456</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136935406</v>
       </c>
       <c r="B4" t="n">
-        <v>92453</v>
+        <v>92456</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136935458</v>
       </c>
       <c r="B5" t="n">
-        <v>92182</v>
+        <v>92185</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136935719</v>
       </c>
       <c r="B6" t="n">
-        <v>92182</v>
+        <v>92185</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>136935946</v>
       </c>
       <c r="B7" t="n">
-        <v>92182</v>
+        <v>92185</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>136935701</v>
       </c>
       <c r="B8" t="n">
-        <v>92614</v>
+        <v>92617</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>136933750</v>
       </c>
       <c r="B9" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>136933934</v>
       </c>
       <c r="B10" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>136934223</v>
       </c>
       <c r="B11" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>136934434</v>
       </c>
       <c r="B12" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         <v>136934718</v>
       </c>
       <c r="B13" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1907,7 +1907,7 @@
         <v>136934843</v>
       </c>
       <c r="B14" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         <v>136935767</v>
       </c>
       <c r="B15" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2111,7 +2111,7 @@
         <v>136944622</v>
       </c>
       <c r="B16" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2213,7 +2213,7 @@
         <v>136933806</v>
       </c>
       <c r="B17" t="n">
-        <v>79290</v>
+        <v>79292</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2315,7 +2315,7 @@
         <v>136934028</v>
       </c>
       <c r="B18" t="n">
-        <v>80648</v>
+        <v>80650</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2417,7 +2417,7 @@
         <v>136934747</v>
       </c>
       <c r="B19" t="n">
-        <v>80648</v>
+        <v>80650</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2519,7 +2519,7 @@
         <v>136944620</v>
       </c>
       <c r="B20" t="n">
-        <v>80648</v>
+        <v>80650</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3392,7 +3392,7 @@
         <v>136933740</v>
       </c>
       <c r="B28" t="n">
-        <v>111427</v>
+        <v>111430</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3494,7 +3494,7 @@
         <v>136934919</v>
       </c>
       <c r="B29" t="n">
-        <v>98293</v>
+        <v>98296</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 40428-2023 artfynd.xlsx
+++ b/artfynd/A 40428-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136944617</v>
       </c>
       <c r="B2" t="n">
-        <v>97671</v>
+        <v>97672</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136934804</v>
       </c>
       <c r="B3" t="n">
-        <v>92456</v>
+        <v>92457</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136935406</v>
       </c>
       <c r="B4" t="n">
-        <v>92456</v>
+        <v>92457</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136935458</v>
       </c>
       <c r="B5" t="n">
-        <v>92185</v>
+        <v>92186</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136935719</v>
       </c>
       <c r="B6" t="n">
-        <v>92185</v>
+        <v>92186</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>136935946</v>
       </c>
       <c r="B7" t="n">
-        <v>92185</v>
+        <v>92186</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>136935701</v>
       </c>
       <c r="B8" t="n">
-        <v>92617</v>
+        <v>92618</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>136933750</v>
       </c>
       <c r="B9" t="n">
-        <v>79535</v>
+        <v>79536</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>136933934</v>
       </c>
       <c r="B10" t="n">
-        <v>79535</v>
+        <v>79536</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>136934223</v>
       </c>
       <c r="B11" t="n">
-        <v>79535</v>
+        <v>79536</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>136934434</v>
       </c>
       <c r="B12" t="n">
-        <v>79535</v>
+        <v>79536</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         <v>136934718</v>
       </c>
       <c r="B13" t="n">
-        <v>79535</v>
+        <v>79536</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1907,7 +1907,7 @@
         <v>136934843</v>
       </c>
       <c r="B14" t="n">
-        <v>79535</v>
+        <v>79536</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         <v>136935767</v>
       </c>
       <c r="B15" t="n">
-        <v>79535</v>
+        <v>79536</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2111,7 +2111,7 @@
         <v>136944622</v>
       </c>
       <c r="B16" t="n">
-        <v>79535</v>
+        <v>79536</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2213,7 +2213,7 @@
         <v>136933806</v>
       </c>
       <c r="B17" t="n">
-        <v>79292</v>
+        <v>79293</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2315,7 +2315,7 @@
         <v>136934028</v>
       </c>
       <c r="B18" t="n">
-        <v>80650</v>
+        <v>80651</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2417,7 +2417,7 @@
         <v>136934747</v>
       </c>
       <c r="B19" t="n">
-        <v>80650</v>
+        <v>80651</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2519,7 +2519,7 @@
         <v>136944620</v>
       </c>
       <c r="B20" t="n">
-        <v>80650</v>
+        <v>80651</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3392,7 +3392,7 @@
         <v>136933740</v>
       </c>
       <c r="B28" t="n">
-        <v>111430</v>
+        <v>111432</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3494,7 +3494,7 @@
         <v>136934919</v>
       </c>
       <c r="B29" t="n">
-        <v>98296</v>
+        <v>98297</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 40428-2023 artfynd.xlsx
+++ b/artfynd/A 40428-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136944617</v>
       </c>
       <c r="B2" t="n">
-        <v>97672</v>
+        <v>97675</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136934804</v>
       </c>
       <c r="B3" t="n">
-        <v>92457</v>
+        <v>92460</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136935406</v>
       </c>
       <c r="B4" t="n">
-        <v>92457</v>
+        <v>92460</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136935458</v>
       </c>
       <c r="B5" t="n">
-        <v>92186</v>
+        <v>92189</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136935719</v>
       </c>
       <c r="B6" t="n">
-        <v>92186</v>
+        <v>92189</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>136935946</v>
       </c>
       <c r="B7" t="n">
-        <v>92186</v>
+        <v>92189</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>136935701</v>
       </c>
       <c r="B8" t="n">
-        <v>92618</v>
+        <v>92621</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>136933750</v>
       </c>
       <c r="B9" t="n">
-        <v>79536</v>
+        <v>79539</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>136933934</v>
       </c>
       <c r="B10" t="n">
-        <v>79536</v>
+        <v>79539</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>136934223</v>
       </c>
       <c r="B11" t="n">
-        <v>79536</v>
+        <v>79539</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>136934434</v>
       </c>
       <c r="B12" t="n">
-        <v>79536</v>
+        <v>79539</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         <v>136934718</v>
       </c>
       <c r="B13" t="n">
-        <v>79536</v>
+        <v>79539</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1907,7 +1907,7 @@
         <v>136934843</v>
       </c>
       <c r="B14" t="n">
-        <v>79536</v>
+        <v>79539</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         <v>136935767</v>
       </c>
       <c r="B15" t="n">
-        <v>79536</v>
+        <v>79539</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2111,7 +2111,7 @@
         <v>136944622</v>
       </c>
       <c r="B16" t="n">
-        <v>79536</v>
+        <v>79539</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2213,7 +2213,7 @@
         <v>136933806</v>
       </c>
       <c r="B17" t="n">
-        <v>79293</v>
+        <v>79296</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2315,7 +2315,7 @@
         <v>136934028</v>
       </c>
       <c r="B18" t="n">
-        <v>80651</v>
+        <v>80654</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2417,7 +2417,7 @@
         <v>136934747</v>
       </c>
       <c r="B19" t="n">
-        <v>80651</v>
+        <v>80654</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2519,7 +2519,7 @@
         <v>136944620</v>
       </c>
       <c r="B20" t="n">
-        <v>80651</v>
+        <v>80654</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2621,7 +2621,7 @@
         <v>136935112</v>
       </c>
       <c r="B21" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2728,7 +2728,7 @@
         <v>119454343</v>
       </c>
       <c r="B22" t="n">
-        <v>58027</v>
+        <v>58030</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2843,7 +2843,7 @@
         <v>136934585</v>
       </c>
       <c r="B23" t="n">
-        <v>57221</v>
+        <v>57224</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2950,7 +2950,7 @@
         <v>136944618</v>
       </c>
       <c r="B24" t="n">
-        <v>57221</v>
+        <v>57224</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3285,7 +3285,7 @@
         <v>136934376</v>
       </c>
       <c r="B27" t="n">
-        <v>58196</v>
+        <v>58199</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3392,7 +3392,7 @@
         <v>136933740</v>
       </c>
       <c r="B28" t="n">
-        <v>111432</v>
+        <v>111436</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3494,7 +3494,7 @@
         <v>136934919</v>
       </c>
       <c r="B29" t="n">
-        <v>98297</v>
+        <v>98300</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
